--- a/results/reliability_eval/Llama-3-8B_P127_sample_30_tokens_0.1_temp_factual_retrieval_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P127_sample_30_tokens_0.1_temp_factual_retrieval_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5985717364237142</v>
+        <v>0.6003556523317003</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8352552992086476</v>
+        <v>0.8632782912219918</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5985717364237142</v>
+        <v>0.6003012157503175</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8352552992086476</v>
+        <v>0.8632648053110653</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4122539747150656</v>
+        <v>0.4002395209580838</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7516738695457575</v>
+        <v>0.7836734700237945</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9983358873671104</v>
+        <v>0.9985302123026674</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9993354144140029</v>
+        <v>0.9995995788016528</v>
       </c>
       <c r="I2" t="n">
-        <v>0.788</v>
+        <v>0.835</v>
       </c>
     </row>
   </sheetData>
